--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.4968675182032</v>
+        <v>5.768240971708019</v>
       </c>
       <c r="D2" t="n">
-        <v>33.42055756253018</v>
+        <v>5.430840603911154</v>
       </c>
       <c r="E2" t="n">
-        <v>8.49365668392347</v>
+        <v>1.380219211137564</v>
       </c>
       <c r="F2" t="n">
-        <v>9.159526482493815</v>
+        <v>1.488423053405245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.782402231345582</v>
+        <v>1.264640362593657</v>
       </c>
       <c r="D3" t="n">
-        <v>6.955186170709942</v>
+        <v>1.130217752740366</v>
       </c>
       <c r="E3" t="n">
-        <v>8.49365668392347</v>
+        <v>1.380219211137564</v>
       </c>
       <c r="F3" t="n">
-        <v>9.159526482493815</v>
+        <v>1.488423053405245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.26785204625448</v>
+        <v>3.618525957516352</v>
       </c>
       <c r="D4" t="n">
-        <v>20.21175379937666</v>
+        <v>3.284409992398707</v>
       </c>
       <c r="E4" t="n">
-        <v>8.49365668392347</v>
+        <v>1.380219211137564</v>
       </c>
       <c r="F4" t="n">
-        <v>9.159526482493815</v>
+        <v>1.488423053405245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.55529219917653</v>
+        <v>4.477734982366186</v>
       </c>
       <c r="D5" t="n">
-        <v>6.272520248195935</v>
+        <v>1.01928454033184</v>
       </c>
       <c r="E5" t="n">
-        <v>8.49365668392347</v>
+        <v>1.380219211137564</v>
       </c>
       <c r="F5" t="n">
-        <v>9.159526482493815</v>
+        <v>1.488423053405245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.13212152385091</v>
+        <v>3.921469747625773</v>
       </c>
       <c r="D6" t="n">
-        <v>23.00147095909736</v>
+        <v>3.737739030853321</v>
       </c>
       <c r="E6" t="n">
-        <v>8.49365668392347</v>
+        <v>1.380219211137564</v>
       </c>
       <c r="F6" t="n">
-        <v>9.159526482493815</v>
+        <v>1.488423053405245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.29603014634542</v>
+        <v>2.160604898781131</v>
       </c>
       <c r="D7" t="n">
-        <v>11.52481855791246</v>
+        <v>1.872783015660775</v>
       </c>
       <c r="E7" t="n">
-        <v>8.49365668392347</v>
+        <v>1.380219211137564</v>
       </c>
       <c r="F7" t="n">
-        <v>9.159526482493815</v>
+        <v>1.488423053405245</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.3717498057065</v>
+        <v>2.985409343427306</v>
       </c>
       <c r="D8" t="n">
-        <v>11.45205270967132</v>
+        <v>1.86095856532159</v>
       </c>
       <c r="E8" t="n">
-        <v>8.49365668392347</v>
+        <v>1.380219211137564</v>
       </c>
       <c r="F8" t="n">
-        <v>9.159526482493815</v>
+        <v>1.488423053405245</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
